--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X309"/>
+  <dimension ref="A1:X312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24363,7 +24363,7 @@
         <v>362.92</v>
       </c>
       <c r="C308" t="n">
-        <v>356.29</v>
+        <v>353.85</v>
       </c>
       <c r="D308" t="n">
         <v>352.22</v>
@@ -24420,10 +24420,10 @@
         <v>339.28</v>
       </c>
       <c r="V308" t="n">
-        <v>336.1</v>
+        <v>343.18</v>
       </c>
       <c r="W308" t="n">
-        <v>335.21</v>
+        <v>341.19</v>
       </c>
       <c r="X308" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>362.75</v>
       </c>
       <c r="C309" t="n">
-        <v>358.16</v>
+        <v>355.63</v>
       </c>
       <c r="D309" t="n">
         <v>354.69</v>
@@ -24498,12 +24498,246 @@
         <v>337.39</v>
       </c>
       <c r="V309" t="n">
-        <v>325.67</v>
+        <v>342.21</v>
       </c>
       <c r="W309" t="n">
-        <v>325.86</v>
+        <v>338.98</v>
       </c>
       <c r="X309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:06:13+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="C310" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="D310" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="E310" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="F310" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="G310" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="H310" t="n">
+        <v>345.97</v>
+      </c>
+      <c r="I310" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="J310" t="n">
+        <v>342</v>
+      </c>
+      <c r="K310" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="L310" t="n">
+        <v>341.51</v>
+      </c>
+      <c r="M310" t="n">
+        <v>347.44</v>
+      </c>
+      <c r="N310" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="O310" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="P310" t="n">
+        <v>319.67</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="R310" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="S310" t="n">
+        <v>303.42</v>
+      </c>
+      <c r="T310" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="U310" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="V310" t="n">
+        <v>342.22</v>
+      </c>
+      <c r="W310" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="C311" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="D311" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="E311" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="F311" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="G311" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="H311" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="I311" t="n">
+        <v>339.97</v>
+      </c>
+      <c r="J311" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="K311" t="n">
+        <v>339.61</v>
+      </c>
+      <c r="L311" t="n">
+        <v>339.82</v>
+      </c>
+      <c r="M311" t="n">
+        <v>344.87</v>
+      </c>
+      <c r="N311" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="O311" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="P311" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>323.26</v>
+      </c>
+      <c r="R311" t="n">
+        <v>319.27</v>
+      </c>
+      <c r="S311" t="n">
+        <v>294.73</v>
+      </c>
+      <c r="T311" t="n">
+        <v>333.89</v>
+      </c>
+      <c r="U311" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="V311" t="n">
+        <v>342.3</v>
+      </c>
+      <c r="W311" t="n">
+        <v>338.37</v>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="C312" t="n">
+        <v>355.76</v>
+      </c>
+      <c r="D312" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="E312" t="n">
+        <v>351.66</v>
+      </c>
+      <c r="F312" t="n">
+        <v>349.1</v>
+      </c>
+      <c r="G312" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="H312" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="I312" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="J312" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="K312" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="L312" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="M312" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="N312" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="O312" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="P312" t="n">
+        <v>306.51</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="R312" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="S312" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="T312" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="U312" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="V312" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="W312" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="X312" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24520,7 +24754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27673,6 +27907,36 @@
       </c>
       <c r="B315" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -27841,28 +28105,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4280204318802369</v>
+        <v>-0.399609003819524</v>
       </c>
       <c r="J2" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05512487029842317</v>
+        <v>0.04866778633565505</v>
       </c>
       <c r="M2" t="n">
-        <v>9.219352968597141</v>
+        <v>9.23920217547716</v>
       </c>
       <c r="N2" t="n">
-        <v>176.3313852676984</v>
+        <v>176.9815451414783</v>
       </c>
       <c r="O2" t="n">
-        <v>13.27898284010106</v>
+        <v>13.30344110151499</v>
       </c>
       <c r="P2" t="n">
-        <v>357.6399768582056</v>
+        <v>357.3404401855958</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27919,28 +28183,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.260053546374155</v>
+        <v>-0.2440990646796947</v>
       </c>
       <c r="J3" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04114018986639745</v>
+        <v>0.03683504037755181</v>
       </c>
       <c r="M3" t="n">
-        <v>7.626303339054409</v>
+        <v>7.632575450498484</v>
       </c>
       <c r="N3" t="n">
-        <v>87.00586236272885</v>
+        <v>86.84059751414792</v>
       </c>
       <c r="O3" t="n">
-        <v>9.327693303423352</v>
+        <v>9.318830265336306</v>
       </c>
       <c r="P3" t="n">
-        <v>351.8486703406394</v>
+        <v>351.6780419121612</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27997,28 +28261,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1876956911100435</v>
+        <v>-0.1603766420735592</v>
       </c>
       <c r="J4" t="n">
+        <v>311</v>
+      </c>
+      <c r="K4" t="n">
         <v>308</v>
       </c>
-      <c r="K4" t="n">
-        <v>305</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01152765434254599</v>
+        <v>0.008496710670492957</v>
       </c>
       <c r="M4" t="n">
-        <v>9.477054285933045</v>
+        <v>9.512318364225983</v>
       </c>
       <c r="N4" t="n">
-        <v>168.0225168442134</v>
+        <v>168.5442528363434</v>
       </c>
       <c r="O4" t="n">
-        <v>12.96234997383628</v>
+        <v>12.98245942941257</v>
       </c>
       <c r="P4" t="n">
-        <v>344.6650755619852</v>
+        <v>344.3743000156595</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28075,28 +28339,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3954315939777878</v>
+        <v>-0.3619793657069468</v>
       </c>
       <c r="J5" t="n">
+        <v>311</v>
+      </c>
+      <c r="K5" t="n">
         <v>308</v>
       </c>
-      <c r="K5" t="n">
-        <v>305</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04892559480820546</v>
+        <v>0.04132888917215949</v>
       </c>
       <c r="M5" t="n">
-        <v>8.901421245549873</v>
+        <v>8.997432518336025</v>
       </c>
       <c r="N5" t="n">
-        <v>172.0092826056543</v>
+        <v>173.6321416413545</v>
       </c>
       <c r="O5" t="n">
-        <v>13.11523093985212</v>
+        <v>13.17695494571316</v>
       </c>
       <c r="P5" t="n">
-        <v>344.126911700549</v>
+        <v>343.7750392704754</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28153,28 +28417,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.108062435847052</v>
+        <v>-0.07736026252863012</v>
       </c>
       <c r="J6" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005667635713990649</v>
+        <v>0.002899468591534449</v>
       </c>
       <c r="M6" t="n">
-        <v>8.433067228261882</v>
+        <v>8.511677905152673</v>
       </c>
       <c r="N6" t="n">
-        <v>115.3565877011726</v>
+        <v>117.0005663047475</v>
       </c>
       <c r="O6" t="n">
-        <v>10.74041841369193</v>
+        <v>10.8166800038065</v>
       </c>
       <c r="P6" t="n">
-        <v>335.8286550554856</v>
+        <v>335.5052701051509</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28231,28 +28495,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2110744010776005</v>
+        <v>-0.1865450541935904</v>
       </c>
       <c r="J7" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K7" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01359044519793595</v>
+        <v>0.01075054979053269</v>
       </c>
       <c r="M7" t="n">
-        <v>10.45584793832178</v>
+        <v>10.46301711120683</v>
       </c>
       <c r="N7" t="n">
-        <v>178.4961480085307</v>
+        <v>178.481689912485</v>
       </c>
       <c r="O7" t="n">
-        <v>13.360245057952</v>
+        <v>13.35970396051069</v>
       </c>
       <c r="P7" t="n">
-        <v>337.849027868057</v>
+        <v>337.5870781762949</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28309,28 +28573,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2408273724927791</v>
+        <v>-0.2171473272285942</v>
       </c>
       <c r="J8" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K8" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0175152183836883</v>
+        <v>0.01443315560653979</v>
       </c>
       <c r="M8" t="n">
-        <v>10.16744451811506</v>
+        <v>10.17366916952543</v>
       </c>
       <c r="N8" t="n">
-        <v>182.6819970133463</v>
+        <v>182.5578908754611</v>
       </c>
       <c r="O8" t="n">
-        <v>13.51599041925327</v>
+        <v>13.51139855364577</v>
       </c>
       <c r="P8" t="n">
-        <v>337.7121403059968</v>
+        <v>337.4624952200099</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28387,28 +28651,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3417945665988225</v>
+        <v>-0.3222341450037998</v>
       </c>
       <c r="J9" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03183940979481847</v>
+        <v>0.0287804758725585</v>
       </c>
       <c r="M9" t="n">
-        <v>10.7266425251021</v>
+        <v>10.70298192335594</v>
       </c>
       <c r="N9" t="n">
-        <v>198.7407408932945</v>
+        <v>197.9273155451424</v>
       </c>
       <c r="O9" t="n">
-        <v>14.09754378937319</v>
+        <v>14.06866431276055</v>
       </c>
       <c r="P9" t="n">
-        <v>338.6616807098924</v>
+        <v>338.4545807284227</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28465,28 +28729,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1368992312669441</v>
+        <v>-0.1195325280613048</v>
       </c>
       <c r="J10" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K10" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005578308319979963</v>
+        <v>0.004321049705216518</v>
       </c>
       <c r="M10" t="n">
-        <v>10.7041642353466</v>
+        <v>10.67606914310398</v>
       </c>
       <c r="N10" t="n">
-        <v>186.4055259711938</v>
+        <v>185.4748246595265</v>
       </c>
       <c r="O10" t="n">
-        <v>13.6530409056442</v>
+        <v>13.61891422469231</v>
       </c>
       <c r="P10" t="n">
-        <v>335.0341131796671</v>
+        <v>334.8500716020231</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28543,28 +28807,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0870438714728886</v>
+        <v>-0.06928598499529701</v>
       </c>
       <c r="J11" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K11" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002541863003070799</v>
+        <v>0.001634383668917216</v>
       </c>
       <c r="M11" t="n">
-        <v>10.45061010308587</v>
+        <v>10.4271766124195</v>
       </c>
       <c r="N11" t="n">
-        <v>166.9524189376869</v>
+        <v>166.2620896135363</v>
       </c>
       <c r="O11" t="n">
-        <v>12.92100688559862</v>
+        <v>12.89426576480942</v>
       </c>
       <c r="P11" t="n">
-        <v>332.2609336121707</v>
+        <v>332.0737217823992</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28621,28 +28885,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05466560233026846</v>
+        <v>0.07254595353267125</v>
       </c>
       <c r="J12" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K12" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0009310721778641451</v>
+        <v>0.00166186230277221</v>
       </c>
       <c r="M12" t="n">
-        <v>11.11172916032457</v>
+        <v>11.07771243407261</v>
       </c>
       <c r="N12" t="n">
-        <v>180.0587199989089</v>
+        <v>179.2568887700893</v>
       </c>
       <c r="O12" t="n">
-        <v>13.41859605170783</v>
+        <v>13.38868510235749</v>
       </c>
       <c r="P12" t="n">
-        <v>328.9291185317003</v>
+        <v>328.740618583812</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28699,28 +28963,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05529769780821784</v>
+        <v>0.0801859860182141</v>
       </c>
       <c r="J13" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K13" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0008766594184909104</v>
+        <v>0.001860260131857916</v>
       </c>
       <c r="M13" t="n">
-        <v>11.17887005836636</v>
+        <v>11.16160739644002</v>
       </c>
       <c r="N13" t="n">
-        <v>194.0372931459019</v>
+        <v>193.9555449374266</v>
       </c>
       <c r="O13" t="n">
-        <v>13.92972695877065</v>
+        <v>13.9267923420085</v>
       </c>
       <c r="P13" t="n">
-        <v>330.3233961447684</v>
+        <v>330.0593281604211</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28777,28 +29041,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1551460387750003</v>
+        <v>-0.1312517178884923</v>
       </c>
       <c r="J14" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K14" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005917040787349226</v>
+        <v>0.004293012308894339</v>
       </c>
       <c r="M14" t="n">
-        <v>11.60132312136458</v>
+        <v>11.58257974737435</v>
       </c>
       <c r="N14" t="n">
-        <v>225.1553928283176</v>
+        <v>224.6296072914312</v>
       </c>
       <c r="O14" t="n">
-        <v>15.00517886692183</v>
+        <v>14.98764849105527</v>
       </c>
       <c r="P14" t="n">
-        <v>337.1547353166629</v>
+        <v>336.9012112319487</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28855,28 +29119,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>0.007654063967720426</v>
+        <v>0.02713054161502111</v>
       </c>
       <c r="J15" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K15" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L15" t="n">
-        <v>1.344266180558495e-05</v>
+        <v>0.0001713799302264229</v>
       </c>
       <c r="M15" t="n">
-        <v>9.811899101395122</v>
+        <v>9.81044665531865</v>
       </c>
       <c r="N15" t="n">
-        <v>241.3366121603548</v>
+        <v>240.1117167049552</v>
       </c>
       <c r="O15" t="n">
-        <v>15.53501246090118</v>
+        <v>15.49553860648139</v>
       </c>
       <c r="P15" t="n">
-        <v>338.2272748429098</v>
+        <v>338.0197030627699</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28933,28 +29197,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6654772242853961</v>
+        <v>-0.6881597399154421</v>
       </c>
       <c r="J16" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K16" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04597416496316376</v>
+        <v>0.049752586760344</v>
       </c>
       <c r="M16" t="n">
-        <v>17.42638554930702</v>
+        <v>17.42686200238235</v>
       </c>
       <c r="N16" t="n">
-        <v>507.2377503429818</v>
+        <v>504.0324484791375</v>
       </c>
       <c r="O16" t="n">
-        <v>22.52193931132445</v>
+        <v>22.45066699408143</v>
       </c>
       <c r="P16" t="n">
-        <v>342.3518553917978</v>
+        <v>342.5948630150565</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29011,28 +29275,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001754158363839941</v>
+        <v>-0.01265075878422591</v>
       </c>
       <c r="J17" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K17" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L17" t="n">
-        <v>2.966399507142725e-07</v>
+        <v>1.570486089907952e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>17.97075187581768</v>
+        <v>17.91070498049272</v>
       </c>
       <c r="N17" t="n">
-        <v>579.4246403574509</v>
+        <v>574.7378518200958</v>
       </c>
       <c r="O17" t="n">
-        <v>24.07124093929208</v>
+        <v>23.97369082598872</v>
       </c>
       <c r="P17" t="n">
-        <v>331.2933739664353</v>
+        <v>331.4089746960531</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29089,28 +29353,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2634481049777674</v>
+        <v>-0.2700306642259291</v>
       </c>
       <c r="J18" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K18" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005065850202748301</v>
+        <v>0.005419346058713748</v>
       </c>
       <c r="M18" t="n">
-        <v>21.64371506939032</v>
+        <v>21.52511741751879</v>
       </c>
       <c r="N18" t="n">
-        <v>761.4147470317446</v>
+        <v>754.7391137940907</v>
       </c>
       <c r="O18" t="n">
-        <v>27.59374470838898</v>
+        <v>27.47251560731362</v>
       </c>
       <c r="P18" t="n">
-        <v>331.644190867784</v>
+        <v>331.7140995547774</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29167,28 +29431,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.48659953238623</v>
+        <v>-0.5356939407460476</v>
       </c>
       <c r="J19" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K19" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01874522524691491</v>
+        <v>0.02282771031431907</v>
       </c>
       <c r="M19" t="n">
-        <v>20.74919188293518</v>
+        <v>20.91024676842953</v>
       </c>
       <c r="N19" t="n">
-        <v>686.3800339896511</v>
+        <v>686.8676792420395</v>
       </c>
       <c r="O19" t="n">
-        <v>26.19885558549554</v>
+        <v>26.20816054670834</v>
       </c>
       <c r="P19" t="n">
-        <v>335.9851880958188</v>
+        <v>336.5086689075309</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29245,28 +29509,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7922731664697581</v>
+        <v>-0.7715334870586531</v>
       </c>
       <c r="J20" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K20" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07238858940856618</v>
+        <v>0.06997577343847305</v>
       </c>
       <c r="M20" t="n">
-        <v>15.50794553736047</v>
+        <v>15.42293392879247</v>
       </c>
       <c r="N20" t="n">
-        <v>449.2985265146339</v>
+        <v>446.2042276002115</v>
       </c>
       <c r="O20" t="n">
-        <v>21.19666309857837</v>
+        <v>21.12354675711945</v>
       </c>
       <c r="P20" t="n">
-        <v>342.9534569614969</v>
+        <v>342.73377235559</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29323,28 +29587,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3754664089855718</v>
+        <v>-0.3556454088093586</v>
       </c>
       <c r="J21" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K21" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03443171355629726</v>
+        <v>0.03143053507322291</v>
       </c>
       <c r="M21" t="n">
-        <v>11.16126476138024</v>
+        <v>11.12534580233486</v>
       </c>
       <c r="N21" t="n">
-        <v>220.828776557175</v>
+        <v>219.8320334320198</v>
       </c>
       <c r="O21" t="n">
-        <v>14.86030876385733</v>
+        <v>14.82673374118588</v>
       </c>
       <c r="P21" t="n">
-        <v>339.238006851947</v>
+        <v>339.0280595778627</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29401,28 +29665,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.758338274971104</v>
+        <v>-0.7100711807508079</v>
       </c>
       <c r="J22" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K22" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05256448271957426</v>
+        <v>0.04685542104351426</v>
       </c>
       <c r="M22" t="n">
-        <v>19.17002915843396</v>
+        <v>19.12742531842094</v>
       </c>
       <c r="N22" t="n">
-        <v>578.9917172695916</v>
+        <v>578.469246908636</v>
       </c>
       <c r="O22" t="n">
-        <v>24.06224672115203</v>
+        <v>24.0513876295867</v>
       </c>
       <c r="P22" t="n">
-        <v>343.8626209944017</v>
+        <v>343.3525133193565</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29479,28 +29743,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.113053726594623</v>
+        <v>-1.074727106104917</v>
       </c>
       <c r="J23" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K23" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1073976565287885</v>
+        <v>0.1021198573118532</v>
       </c>
       <c r="M23" t="n">
-        <v>19.74065006150096</v>
+        <v>19.69699021769597</v>
       </c>
       <c r="N23" t="n">
-        <v>567.5599517106901</v>
+        <v>565.1717741202243</v>
       </c>
       <c r="O23" t="n">
-        <v>23.82351677881941</v>
+        <v>23.77334166919376</v>
       </c>
       <c r="P23" t="n">
-        <v>354.0253427267902</v>
+        <v>353.6152955959247</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29538,7 +29802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X309"/>
+  <dimension ref="A1:X312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66872,7 +67136,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>-39.86365792258433,174.81739375074</t>
+          <t>-39.86363714650571,174.8174030525521</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -66967,12 +67231,12 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>-39.85905180794429,174.80140997523515</t>
+          <t>-39.85911209049508,174.80138297699452</t>
         </is>
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>-39.85881084312461,174.8005680668145</t>
+          <t>-39.858861759647766,174.80054526287535</t>
         </is>
       </c>
       <c r="X308" t="inlineStr">
@@ -66994,7 +67258,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>-39.86367384523429,174.81738662188852</t>
+          <t>-39.86365230282543,174.81739626680448</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -67089,15 +67353,381 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>-39.85896300185956,174.80144974798415</t>
+          <t>-39.859103831445395,174.8013866759087</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>-39.858731232833414,174.80060372173787</t>
+          <t>-39.858842942672304,174.80055369042185</t>
         </is>
       </c>
       <c r="X309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:06:13+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-39.863951238177336,174.81821221659942</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-39.86365715625357,174.8173940938397</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-39.86342506128793,174.81654821850873</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-39.863169975686866,174.81571263646404</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-39.86291855071035,174.81487541538328</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-39.862647626291036,174.8140469250448</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-39.862403181957475,174.81320657832856</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-39.86213472544036,174.81237698317295</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-39.86190262592689,174.81153110862843</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-39.86165886053042,174.81069045742686</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-39.86143169793531,174.8098423715443</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-39.86124881058762,174.80897445906115</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-39.861019773060114,174.80812721152896</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-39.860819769492196,174.80726696190496</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-39.86031221834866,174.8065444359135</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-39.86021404773806,174.80563858397537</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>-39.859943711629796,174.80480983042418</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>-39.85947370900973,174.80407049488198</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>-39.859482392749285,174.80311678592147</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>-39.859310482160126,174.80224395219648</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>-39.85910391659025,174.80138663777555</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>-39.858838770582636,174.8005555589723</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-39.863932505614144,174.81822060336532</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-39.863639104906596,174.8174021757422</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-39.863402582294185,174.8165582829182</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-39.86314988086583,174.8157216335685</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-39.86289922225294,174.81488406950578</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-39.86262880875213,174.81405535054392</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-39.862384364453526,174.81321500395384</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-39.8621187178191,174.81238415077598</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-39.86189138655438,174.81153614127817</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-39.86164889837788,174.81069491825156</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-39.861417308186496,174.8098488150569</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-39.86122692799456,174.80898425793808</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-39.861000359745674,174.8081359048302</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-39.86078477450562,174.8072826329749</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-39.860236779140536,174.80657821855516</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-39.86010940372581,174.80568544587248</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>-39.85984204790057,174.80485535841797</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>-39.85939971768106,174.80410363071476</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>-39.85949976236465,174.80310900701755</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>-39.85932316876593,174.8022382704499</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>-39.859104597748974,174.80138633271054</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>-39.85883774884638,174.80055601657645</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-39.86393914715934,174.8182176298761</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-39.86365340974765,174.81739577121604</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-39.86340683967943,174.8165563767805</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-39.86315175411189,174.81572079485557</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-39.86289658268381,174.8148852513459</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-39.86262676521846,174.81405626553</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-39.862384875336005,174.8132147752039</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-39.86211480106064,174.8123859045507</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-39.86188891729828,174.81153724693587</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-39.86164481134088,174.8106967483331</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-39.86141586069695,174.80984946322076</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-39.86122224494923,174.8089863549732</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-39.86099584700144,174.80813792564078</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-39.860785115089456,174.80728248045847</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-39.86020016642901,174.80659461416823</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-39.86005508078983,174.80570977282443</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>-39.859785681571196,174.80488060085116</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>-39.859361402260014,174.80412078963457</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>-39.85950623339769,174.80310610899352</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>-39.859328532901195,174.80223586810004</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>-39.859117028895874,174.80138076527223</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>-39.85885801328165,174.80054694075824</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X312"/>
+  <dimension ref="A1:X313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24561,10 +24561,10 @@
         <v>319.67</v>
       </c>
       <c r="Q310" t="n">
-        <v>335.55</v>
+        <v>349.58</v>
       </c>
       <c r="R310" t="n">
-        <v>331.21</v>
+        <v>345.06</v>
       </c>
       <c r="S310" t="n">
         <v>303.42</v>
@@ -24639,10 +24639,10 @@
         <v>310.81</v>
       </c>
       <c r="Q311" t="n">
-        <v>323.26</v>
+        <v>349.58</v>
       </c>
       <c r="R311" t="n">
-        <v>319.27</v>
+        <v>345.06</v>
       </c>
       <c r="S311" t="n">
         <v>294.73</v>
@@ -24717,10 +24717,10 @@
         <v>306.51</v>
       </c>
       <c r="Q312" t="n">
-        <v>316.88</v>
+        <v>349.58</v>
       </c>
       <c r="R312" t="n">
-        <v>312.65</v>
+        <v>345.06</v>
       </c>
       <c r="S312" t="n">
         <v>290.23</v>
@@ -24738,6 +24738,84 @@
         <v>340.75</v>
       </c>
       <c r="X312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="C313" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="D313" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="E313" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="F313" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="G313" t="n">
+        <v>344.45</v>
+      </c>
+      <c r="H313" t="n">
+        <v>343.19</v>
+      </c>
+      <c r="I313" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="J313" t="n">
+        <v>339.91</v>
+      </c>
+      <c r="K313" t="n">
+        <v>338.63</v>
+      </c>
+      <c r="L313" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="M313" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="N313" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="O313" t="n">
+        <v>347.88</v>
+      </c>
+      <c r="P313" t="n">
+        <v>306.51</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="R313" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="S313" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="T313" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="U313" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="V313" t="n">
+        <v>343.66</v>
+      </c>
+      <c r="W313" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="X313" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24754,7 +24832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27937,6 +28015,16 @@
       </c>
       <c r="B318" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -28105,28 +28193,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.399609003819524</v>
+        <v>-0.3899302595190393</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04866778633565505</v>
+        <v>0.0465205342071211</v>
       </c>
       <c r="M2" t="n">
-        <v>9.23920217547716</v>
+        <v>9.249228430801203</v>
       </c>
       <c r="N2" t="n">
-        <v>176.9815451414783</v>
+        <v>177.2477487829281</v>
       </c>
       <c r="O2" t="n">
-        <v>13.30344110151499</v>
+        <v>13.3134424091941</v>
       </c>
       <c r="P2" t="n">
-        <v>357.3404401855958</v>
+        <v>357.2380362686853</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28183,28 +28271,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2440990646796947</v>
+        <v>-0.2369028915432032</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03683504037755181</v>
+        <v>0.03481070919707041</v>
       </c>
       <c r="M3" t="n">
-        <v>7.632575450498484</v>
+        <v>7.644067480248249</v>
       </c>
       <c r="N3" t="n">
-        <v>86.84059751414792</v>
+        <v>87.01066819797096</v>
       </c>
       <c r="O3" t="n">
-        <v>9.318830265336306</v>
+        <v>9.327950910997064</v>
       </c>
       <c r="P3" t="n">
-        <v>351.6780419121612</v>
+        <v>351.6009204996968</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28261,28 +28349,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1603766420735592</v>
+        <v>-0.1515582323925256</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008496710670492957</v>
+        <v>0.007612290533432375</v>
       </c>
       <c r="M4" t="n">
-        <v>9.512318364225983</v>
+        <v>9.522741340594912</v>
       </c>
       <c r="N4" t="n">
-        <v>168.5442528363434</v>
+        <v>168.6839210133909</v>
       </c>
       <c r="O4" t="n">
-        <v>12.98245942941257</v>
+        <v>12.98783742635358</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3743000156595</v>
+        <v>344.2801032922845</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28339,28 +28427,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3619793657069468</v>
+        <v>-0.3514023655620717</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04132888917215949</v>
+        <v>0.03906219808807332</v>
       </c>
       <c r="M5" t="n">
-        <v>8.997432518336025</v>
+        <v>9.026863178635395</v>
       </c>
       <c r="N5" t="n">
-        <v>173.6321416413545</v>
+        <v>174.0774036796055</v>
       </c>
       <c r="O5" t="n">
-        <v>13.17695494571316</v>
+        <v>13.19383961095501</v>
       </c>
       <c r="P5" t="n">
-        <v>343.7750392704754</v>
+        <v>343.6633804286222</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28417,28 +28505,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07736026252863012</v>
+        <v>-0.06845520717311272</v>
       </c>
       <c r="J6" t="n">
+        <v>312</v>
+      </c>
+      <c r="K6" t="n">
         <v>311</v>
       </c>
-      <c r="K6" t="n">
-        <v>310</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.002899468591534449</v>
+        <v>0.002272492823257033</v>
       </c>
       <c r="M6" t="n">
-        <v>8.511677905152673</v>
+        <v>8.531268111408995</v>
       </c>
       <c r="N6" t="n">
-        <v>117.0005663047475</v>
+        <v>117.332718644463</v>
       </c>
       <c r="O6" t="n">
-        <v>10.8166800038065</v>
+        <v>10.83202283253054</v>
       </c>
       <c r="P6" t="n">
-        <v>335.5052701051509</v>
+        <v>335.4111356293711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28495,28 +28583,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1865450541935904</v>
+        <v>-0.1793821355861689</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01075054979053269</v>
+        <v>0.009987419330460656</v>
       </c>
       <c r="M7" t="n">
-        <v>10.46301711120683</v>
+        <v>10.46096356942309</v>
       </c>
       <c r="N7" t="n">
-        <v>178.481689912485</v>
+        <v>178.3519928929071</v>
       </c>
       <c r="O7" t="n">
-        <v>13.35970396051069</v>
+        <v>13.35484904043872</v>
       </c>
       <c r="P7" t="n">
-        <v>337.5870781762949</v>
+        <v>337.5103131527339</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28573,28 +28661,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2171473272285942</v>
+        <v>-0.2102822053825909</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01443315560653979</v>
+        <v>0.01360165010509828</v>
       </c>
       <c r="M8" t="n">
-        <v>10.17366916952543</v>
+        <v>10.17205419621326</v>
       </c>
       <c r="N8" t="n">
-        <v>182.5578908754611</v>
+        <v>182.3920832298612</v>
       </c>
       <c r="O8" t="n">
-        <v>13.51139855364577</v>
+        <v>13.50526131660773</v>
       </c>
       <c r="P8" t="n">
-        <v>337.4624952200099</v>
+        <v>337.389860243274</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28651,28 +28739,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3222341450037998</v>
+        <v>-0.3164718788839064</v>
       </c>
       <c r="J9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0287804758725585</v>
+        <v>0.02792098445260061</v>
       </c>
       <c r="M9" t="n">
-        <v>10.70298192335594</v>
+        <v>10.69186898306701</v>
       </c>
       <c r="N9" t="n">
-        <v>197.9273155451424</v>
+        <v>197.5830356119116</v>
       </c>
       <c r="O9" t="n">
-        <v>14.06866431276055</v>
+        <v>14.05642328659434</v>
       </c>
       <c r="P9" t="n">
-        <v>338.4545807284227</v>
+        <v>338.3933505103248</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28729,28 +28817,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1195325280613048</v>
+        <v>-0.1145888481674848</v>
       </c>
       <c r="J10" t="n">
+        <v>312</v>
+      </c>
+      <c r="K10" t="n">
         <v>311</v>
       </c>
-      <c r="K10" t="n">
-        <v>310</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.004321049705216518</v>
+        <v>0.003993105354457738</v>
       </c>
       <c r="M10" t="n">
-        <v>10.67606914310398</v>
+        <v>10.6631958642881</v>
       </c>
       <c r="N10" t="n">
-        <v>185.4748246595265</v>
+        <v>185.0941215185764</v>
       </c>
       <c r="O10" t="n">
-        <v>13.61891422469231</v>
+        <v>13.60493004460429</v>
       </c>
       <c r="P10" t="n">
-        <v>334.8500716020231</v>
+        <v>334.7974941356132</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28807,28 +28895,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06928598499529701</v>
+        <v>-0.06427262430389584</v>
       </c>
       <c r="J11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001634383668917216</v>
+        <v>0.001413816998059203</v>
       </c>
       <c r="M11" t="n">
-        <v>10.4271766124195</v>
+        <v>10.41577543640335</v>
       </c>
       <c r="N11" t="n">
-        <v>166.2620896135363</v>
+        <v>165.9528131082056</v>
       </c>
       <c r="O11" t="n">
-        <v>12.89426576480942</v>
+        <v>12.88226739002904</v>
       </c>
       <c r="P11" t="n">
-        <v>332.0737217823992</v>
+        <v>332.020678974805</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28885,28 +28973,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07254595353267125</v>
+        <v>0.07767573427306515</v>
       </c>
       <c r="J12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00166186230277221</v>
+        <v>0.001914381173448443</v>
       </c>
       <c r="M12" t="n">
-        <v>11.07771243407261</v>
+        <v>11.06293446670124</v>
       </c>
       <c r="N12" t="n">
-        <v>179.2568887700893</v>
+        <v>178.9164684009505</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38868510235749</v>
+        <v>13.3759660735571</v>
       </c>
       <c r="P12" t="n">
-        <v>328.740618583812</v>
+        <v>328.6863440183932</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28963,28 +29051,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0801859860182141</v>
+        <v>0.08731219174888322</v>
       </c>
       <c r="J13" t="n">
+        <v>312</v>
+      </c>
+      <c r="K13" t="n">
         <v>311</v>
       </c>
-      <c r="K13" t="n">
-        <v>310</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.001860260131857916</v>
+        <v>0.002213840070554807</v>
       </c>
       <c r="M13" t="n">
-        <v>11.16160739644002</v>
+        <v>11.15200643458518</v>
       </c>
       <c r="N13" t="n">
-        <v>193.9555449374266</v>
+        <v>193.7785615286525</v>
       </c>
       <c r="O13" t="n">
-        <v>13.9267923420085</v>
+        <v>13.92043682966352</v>
       </c>
       <c r="P13" t="n">
-        <v>330.0593281604211</v>
+        <v>329.9834457982828</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29041,28 +29129,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1312517178884923</v>
+        <v>-0.1246320102429417</v>
       </c>
       <c r="J14" t="n">
+        <v>312</v>
+      </c>
+      <c r="K14" t="n">
         <v>311</v>
       </c>
-      <c r="K14" t="n">
-        <v>310</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.004293012308894339</v>
+        <v>0.003890592189920605</v>
       </c>
       <c r="M14" t="n">
-        <v>11.58257974737435</v>
+        <v>11.57192082286555</v>
       </c>
       <c r="N14" t="n">
-        <v>224.6296072914312</v>
+        <v>224.2927556819965</v>
       </c>
       <c r="O14" t="n">
-        <v>14.98764849105527</v>
+        <v>14.97640663450337</v>
       </c>
       <c r="P14" t="n">
-        <v>336.9012112319487</v>
+        <v>336.8307222407808</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29119,28 +29207,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02713054161502111</v>
+        <v>0.0326597581829139</v>
       </c>
       <c r="J15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K15" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001713799302264229</v>
+        <v>0.000249648816388004</v>
       </c>
       <c r="M15" t="n">
-        <v>9.81044665531865</v>
+        <v>9.805886369607684</v>
       </c>
       <c r="N15" t="n">
-        <v>240.1117167049552</v>
+        <v>239.6043012898245</v>
       </c>
       <c r="O15" t="n">
-        <v>15.49553860648139</v>
+        <v>15.47915699545116</v>
       </c>
       <c r="P15" t="n">
-        <v>338.0197030627699</v>
+        <v>337.9605577729528</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29197,28 +29285,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6881597399154421</v>
+        <v>-0.6989761024546891</v>
       </c>
       <c r="J16" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K16" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L16" t="n">
-        <v>0.049752586760344</v>
+        <v>0.05146052251514255</v>
       </c>
       <c r="M16" t="n">
-        <v>17.42686200238235</v>
+        <v>17.45101430060106</v>
       </c>
       <c r="N16" t="n">
-        <v>504.0324484791375</v>
+        <v>503.4163220493049</v>
       </c>
       <c r="O16" t="n">
-        <v>22.45066699408143</v>
+        <v>22.4369410136343</v>
       </c>
       <c r="P16" t="n">
-        <v>342.5948630150565</v>
+        <v>342.711079499274</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29275,28 +29363,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01265075878422591</v>
+        <v>0.0413879243758239</v>
       </c>
       <c r="J17" t="n">
+        <v>312</v>
+      </c>
+      <c r="K17" t="n">
         <v>311</v>
       </c>
-      <c r="K17" t="n">
-        <v>310</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.570486089907952e-05</v>
+        <v>0.0001682252662785766</v>
       </c>
       <c r="M17" t="n">
-        <v>17.91070498049272</v>
+        <v>17.85530045565131</v>
       </c>
       <c r="N17" t="n">
-        <v>574.7378518200958</v>
+        <v>576.0131442492378</v>
       </c>
       <c r="O17" t="n">
-        <v>23.97369082598872</v>
+        <v>24.00027383696357</v>
       </c>
       <c r="P17" t="n">
-        <v>331.4089746960531</v>
+        <v>330.8360842809697</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29353,28 +29441,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2700306642259291</v>
+        <v>-0.2153490256673778</v>
       </c>
       <c r="J18" t="n">
+        <v>312</v>
+      </c>
+      <c r="K18" t="n">
         <v>311</v>
       </c>
-      <c r="K18" t="n">
-        <v>310</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.005419346058713748</v>
+        <v>0.003455736322008574</v>
       </c>
       <c r="M18" t="n">
-        <v>21.52511741751879</v>
+        <v>21.51279699060599</v>
       </c>
       <c r="N18" t="n">
-        <v>754.7391137940907</v>
+        <v>756.6433302675022</v>
       </c>
       <c r="O18" t="n">
-        <v>27.47251560731362</v>
+        <v>27.50715052977138</v>
       </c>
       <c r="P18" t="n">
-        <v>331.7140995547774</v>
+        <v>331.1343555138399</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29431,28 +29519,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5356939407460476</v>
+        <v>-0.5550762725442323</v>
       </c>
       <c r="J19" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K19" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02282771031431907</v>
+        <v>0.02450693420495276</v>
       </c>
       <c r="M19" t="n">
-        <v>20.91024676842953</v>
+        <v>20.98464139695067</v>
       </c>
       <c r="N19" t="n">
-        <v>686.8676792420395</v>
+        <v>687.9346025982672</v>
       </c>
       <c r="O19" t="n">
-        <v>26.20816054670834</v>
+        <v>26.22850744129881</v>
       </c>
       <c r="P19" t="n">
-        <v>336.5086689075309</v>
+        <v>336.7159991174184</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29509,28 +29597,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7715334870586531</v>
+        <v>-0.7642630247686339</v>
       </c>
       <c r="J20" t="n">
+        <v>312</v>
+      </c>
+      <c r="K20" t="n">
         <v>311</v>
       </c>
-      <c r="K20" t="n">
-        <v>310</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.06997577343847305</v>
+        <v>0.06909541078770698</v>
       </c>
       <c r="M20" t="n">
-        <v>15.42293392879247</v>
+        <v>15.39638556160899</v>
       </c>
       <c r="N20" t="n">
-        <v>446.2042276002115</v>
+        <v>445.2368031143811</v>
       </c>
       <c r="O20" t="n">
-        <v>21.12354675711945</v>
+        <v>21.10063513533138</v>
       </c>
       <c r="P20" t="n">
-        <v>342.73377235559</v>
+        <v>342.6565021703526</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29587,28 +29675,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3556454088093586</v>
+        <v>-0.3488614256511547</v>
       </c>
       <c r="J21" t="n">
+        <v>312</v>
+      </c>
+      <c r="K21" t="n">
         <v>311</v>
       </c>
-      <c r="K21" t="n">
-        <v>310</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03143053507322291</v>
+        <v>0.03041197372726401</v>
       </c>
       <c r="M21" t="n">
-        <v>11.12534580233486</v>
+        <v>11.11486590573394</v>
       </c>
       <c r="N21" t="n">
-        <v>219.8320334320198</v>
+        <v>219.5320482642837</v>
       </c>
       <c r="O21" t="n">
-        <v>14.82673374118588</v>
+        <v>14.81661392708481</v>
       </c>
       <c r="P21" t="n">
-        <v>339.0280595778627</v>
+        <v>338.9559596735689</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29665,28 +29753,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7100711807508079</v>
+        <v>-0.6985758152003076</v>
       </c>
       <c r="J22" t="n">
+        <v>312</v>
+      </c>
+      <c r="K22" t="n">
         <v>311</v>
       </c>
-      <c r="K22" t="n">
-        <v>310</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.04685542104351426</v>
+        <v>0.04560816554306679</v>
       </c>
       <c r="M22" t="n">
-        <v>19.12742531842094</v>
+        <v>19.10024553036303</v>
       </c>
       <c r="N22" t="n">
-        <v>578.469246908636</v>
+        <v>577.7774569308766</v>
       </c>
       <c r="O22" t="n">
-        <v>24.0513876295867</v>
+        <v>24.03700182907337</v>
       </c>
       <c r="P22" t="n">
-        <v>343.3525133193565</v>
+        <v>343.230341029614</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29743,28 +29831,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.074727106104917</v>
+        <v>-1.064483374474813</v>
       </c>
       <c r="J23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K23" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1021198573118532</v>
+        <v>0.1008094363937352</v>
       </c>
       <c r="M23" t="n">
-        <v>19.69699021769597</v>
+        <v>19.67228024987588</v>
       </c>
       <c r="N23" t="n">
-        <v>565.1717741202243</v>
+        <v>564.2433253371549</v>
       </c>
       <c r="O23" t="n">
-        <v>23.77334166919376</v>
+        <v>23.7538065441553</v>
       </c>
       <c r="P23" t="n">
-        <v>353.6152955959247</v>
+        <v>353.5050786936151</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29802,7 +29890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X312"/>
+  <dimension ref="A1:X313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67450,12 +67538,12 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>-39.86021404773806,174.80563858397537</t>
+          <t>-39.86033350707314,174.80558508727256</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>-39.859943711629796,174.80480983042418</t>
+          <t>-39.86006163812912,174.80475701931445</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -67572,12 +67660,12 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>-39.86010940372581,174.80568544587248</t>
+          <t>-39.86033350707314,174.80558508727256</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>-39.85984204790057,174.80485535841797</t>
+          <t>-39.86006163812912,174.80475701931445</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -67694,12 +67782,12 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>-39.86005508078983,174.80570977282443</t>
+          <t>-39.86033350707314,174.80558508727256</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>-39.859785681571196,174.80488060085116</t>
+          <t>-39.86006163812912,174.80475701931445</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -67728,6 +67816,128 @@
         </is>
       </c>
       <c r="X312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-39.863947917404815,174.8182137033446</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-39.86366456411751,174.81739077720874</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-39.86341135250776,174.81655435627434</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-39.863153712505486,174.8157199180193</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-39.86289036692423,174.81488803438853</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-39.862623614770705,174.81405767613344</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-39.862379511070074,174.8132171770782</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-39.86211471591372,174.81238594267623</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-39.861884830253665,174.8115390769898</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-39.86164055401066,174.81069865466785</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-39.86141245483919,174.80985098831204</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-39.86121977570716,174.80898746068252</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-39.86098971648092,174.80814067089244</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-39.86078579625709,174.80728217542563</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-39.86020016642901,174.80659461416823</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-39.86032431134468,174.80558920534298</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>-39.86005286814475,174.8047609467893</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>-39.859361402260014,174.80412078963457</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>-39.85950384933289,174.80310717668664</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>-39.85932597855109,174.8022370120762</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>-39.859116177447476,174.80138114660366</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>-39.858867804920315,174.80054255538207</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
